--- a/asx_eod_output/Report_XLSX/Report_20260824.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260824.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.822</v>
+        <v>1.83</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>279095.78</v>
+        <v>280321.23</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>4135.89</v>
+        <v>5361.34</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.395</v>
+        <v>2.38</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>167650</v>
+        <v>166600</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>350</v>
+        <v>-700</v>
       </c>
     </row>
     <row r="6">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>67.28</v>
+        <v>67.17</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>744453.2</v>
+        <v>743236.05</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>23457.8</v>
+        <v>22240.65</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>155.12</v>
+        <v>155.04</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.87</v>
+        <v>-2.95</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>170.745</v>
+        <v>170.12</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2.445</v>
+        <v>1.82</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>682980</v>
+        <v>680480</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9780</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="12">
@@ -785,24 +785,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>6000</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>33.63</v>
+        <v>33.59</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>33.54</v>
+        <v>33.51</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>43199.52</v>
+        <v>43160.88</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-309.12</v>
+        <v>-347.76</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1934196.09</v>
+        <v>1931215.75</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-31711.29</v>
+        <v>-34691.63</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260824.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260824.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.83</v>
+        <v>1.847</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.035</v>
+        <v>0.052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>280321.23</v>
+        <v>282925.31</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5361.34</v>
+        <v>7965.41</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>166600</v>
+        <v>167300</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>67.17</v>
+        <v>67.59</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2.01</v>
+        <v>2.43</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>743236.05</v>
+        <v>747883.35</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>22240.65</v>
+        <v>26887.95</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>155.04</v>
+        <v>157.26</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-2.95</v>
+        <v>-0.73</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.005</v>
+        <v>1.015</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10050</v>
+        <v>10150</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>170.12</v>
+        <v>169.48</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.82</v>
+        <v>1.18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>680480</v>
+        <v>677920</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>7280</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.28</v>
+        <v>0.265</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-5.36%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="13">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>33.59</v>
+        <v>33.87</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.24</v>
+        <v>0.04</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>33.51</v>
+        <v>33.4</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.38</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>43160.88</v>
+        <v>43019.2</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-347.76</v>
+        <v>-489.44</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1931215.75</v>
+        <v>1936265.45</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-34691.63</v>
+        <v>-29641.94</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260824.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260824.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.847</v>
+        <v>1.835</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>282925.31</v>
+        <v>281087.14</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7965.41</v>
+        <v>6127.24</v>
       </c>
     </row>
     <row r="5">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>67.59</v>
+        <v>67.605</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2.43</v>
+        <v>2.445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>747883.35</v>
+        <v>748049.33</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>26887.95</v>
+        <v>27053.93</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>157.26</v>
+        <v>156.97</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.73</v>
+        <v>-1.02</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>169.48</v>
+        <v>169.81</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>677920</v>
+        <v>679240</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4720</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="12">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>33.87</v>
+        <v>33.86</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1936265.45</v>
+        <v>1935913.25</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-29641.94</v>
+        <v>-29994.13</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260824.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260824.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.835</v>
+        <v>1.84</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>281087.14</v>
+        <v>281853.04</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6127.24</v>
+        <v>6893.15</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>167300</v>
+        <v>165900</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
     </row>
     <row r="6">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>67.605</v>
+        <v>67.12</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2.445</v>
+        <v>1.96</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>748049.33</v>
+        <v>742682.8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>27053.93</v>
+        <v>21687.4</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>156.97</v>
+        <v>156.48</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-1.02</v>
+        <v>-1.51</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>169.81</v>
+        <v>169.17</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.51</v>
+        <v>0.87</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>679240</v>
+        <v>676680</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6040</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.265</v>
+        <v>0.285</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-5.36%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5300</v>
+        <v>5700</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>33.86</v>
+        <v>33.72</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1935913.25</v>
+        <v>1927752.63</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-29994.13</v>
+        <v>-38154.75</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260824.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260824.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.045</v>
+        <v>0.055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>281853.04</v>
+        <v>283384.85</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6893.15</v>
+        <v>8424.959999999999</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>165900</v>
+        <v>164500</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-1400</v>
+        <v>-2800</v>
       </c>
     </row>
     <row r="6">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>156.48</v>
+        <v>156.88</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-1.51</v>
+        <v>-1.11</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-0.70%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.015</v>
+        <v>1.01</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10150</v>
+        <v>10100</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>169.17</v>
+        <v>169.11</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>676680</v>
+        <v>676440</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3480</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>33.72</v>
+        <v>33.74</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>33.4</v>
+        <v>33.48</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>43019.2</v>
+        <v>43122.24</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-489.44</v>
+        <v>-386.4</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1927752.63</v>
+        <v>1927597.48</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-38154.75</v>
+        <v>-38309.9</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260824.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260824.xlsx
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-1.17</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>67225.86</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-67225.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -731,24 +731,24 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>700000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1927597.48</v>
+        <v>1996223.34</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-38309.9</v>
+        <v>30315.96</v>
       </c>
     </row>
   </sheetData>
